--- a/source/Data_Master.xlsx
+++ b/source/Data_Master.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22600" windowHeight="12100"/>
+    <workbookView windowWidth="25180" windowHeight="12100"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Master_2015_2026_UPDATED_t" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data_Master_2015_2026_UPDATED_t!$A$1:$L$201</definedName>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="27">
   <si>
     <t>Division</t>
   </si>
@@ -9257,1056 +9256,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="1" max="1" width="9.23076923076923" customWidth="1"/>
-    <col min="2" max="2" width="20.7692307692308" customWidth="1"/>
-    <col min="3" max="3" width="14.3846153846154" customWidth="1"/>
-    <col min="4" max="4" width="6.53846153846154" customWidth="1"/>
-    <col min="5" max="5" width="5.84615384615385" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="16.7692307692308" customWidth="1"/>
-    <col min="8" max="8" width="22.2307692307692" customWidth="1"/>
-    <col min="9" max="9" width="18.6153846153846" customWidth="1"/>
-    <col min="10" max="10" width="18.6923076923077" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12.0769230769231" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>27</v>
-      </c>
-      <c r="E2">
-        <v>2026</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C2,Data_Master_2015_2026_UPDATED_t!$E:$E,$E2)</f>
-        <v>556</v>
-      </c>
-      <c r="H2">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C2,Data_Master_2015_2026_UPDATED_t!$E:$E,$E2)</f>
-        <v>200</v>
-      </c>
-      <c r="I2">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C2,Data_Master_2015_2026_UPDATED_t!$E:$E,$E2)</f>
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C2,Data_Master_2015_2026_UPDATED_t!$E:$E,$E2)</f>
-        <v>20962</v>
-      </c>
-      <c r="K2">
-        <f>L2/J2</f>
-        <v>0.0367331361511306</v>
-      </c>
-      <c r="L2">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C2,Data_Master_2015_2026_UPDATED_t!$E:$E,$E2)</f>
-        <v>770</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3">
-        <v>27</v>
-      </c>
-      <c r="E3">
-        <v>2025</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C3,Data_Master_2015_2026_UPDATED_t!$E:$E,$E3)</f>
-        <v>3798</v>
-      </c>
-      <c r="H3">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C3,Data_Master_2015_2026_UPDATED_t!$E:$E,$E3)</f>
-        <v>272</v>
-      </c>
-      <c r="I3">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C3,Data_Master_2015_2026_UPDATED_t!$E:$E,$E3)</f>
-        <v>60</v>
-      </c>
-      <c r="J3">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C3,Data_Master_2015_2026_UPDATED_t!$E:$E,$E3)</f>
-        <v>20902</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K12" si="0">L3/J3</f>
-        <v>0.197588747488279</v>
-      </c>
-      <c r="L3">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C3,Data_Master_2015_2026_UPDATED_t!$E:$E,$E3)</f>
-        <v>4130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>27</v>
-      </c>
-      <c r="E4">
-        <v>2025</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C4,Data_Master_2015_2026_UPDATED_t!$E:$E,$E4)</f>
-        <v>282</v>
-      </c>
-      <c r="H4">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C4,Data_Master_2015_2026_UPDATED_t!$E:$E,$E4)</f>
-        <v>98</v>
-      </c>
-      <c r="I4">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C4,Data_Master_2015_2026_UPDATED_t!$E:$E,$E4)</f>
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C4,Data_Master_2015_2026_UPDATED_t!$E:$E,$E4)</f>
-        <v>20350</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>0.0191646191646192</v>
-      </c>
-      <c r="L4">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C4,Data_Master_2015_2026_UPDATED_t!$E:$E,$E4)</f>
-        <v>390</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5">
-        <v>27</v>
-      </c>
-      <c r="E5">
-        <v>2024</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C5,Data_Master_2015_2026_UPDATED_t!$E:$E,$E5)</f>
-        <v>9116</v>
-      </c>
-      <c r="H5">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C5,Data_Master_2015_2026_UPDATED_t!$E:$E,$E5)</f>
-        <v>2492</v>
-      </c>
-      <c r="I5">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C5,Data_Master_2015_2026_UPDATED_t!$E:$E,$E5)</f>
-        <v>170</v>
-      </c>
-      <c r="J5">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C5,Data_Master_2015_2026_UPDATED_t!$E:$E,$E5)</f>
-        <v>23324</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>0.504973417938604</v>
-      </c>
-      <c r="L5">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C5,Data_Master_2015_2026_UPDATED_t!$E:$E,$E5)</f>
-        <v>11778</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>27</v>
-      </c>
-      <c r="E6">
-        <v>2024</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C6,Data_Master_2015_2026_UPDATED_t!$E:$E,$E6)</f>
-        <v>1326</v>
-      </c>
-      <c r="H6">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C6,Data_Master_2015_2026_UPDATED_t!$E:$E,$E6)</f>
-        <v>126</v>
-      </c>
-      <c r="I6">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C6,Data_Master_2015_2026_UPDATED_t!$E:$E,$E6)</f>
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C6,Data_Master_2015_2026_UPDATED_t!$E:$E,$E6)</f>
-        <v>17712</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0.0829945799457995</v>
-      </c>
-      <c r="L6">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C6,Data_Master_2015_2026_UPDATED_t!$E:$E,$E6)</f>
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>27</v>
-      </c>
-      <c r="E7">
-        <v>2023</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C7,Data_Master_2015_2026_UPDATED_t!$E:$E,$E7)</f>
-        <v>2330</v>
-      </c>
-      <c r="H7">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C7,Data_Master_2015_2026_UPDATED_t!$E:$E,$E7)</f>
-        <v>206</v>
-      </c>
-      <c r="I7">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C7,Data_Master_2015_2026_UPDATED_t!$E:$E,$E7)</f>
-        <v>162</v>
-      </c>
-      <c r="J7">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C7,Data_Master_2015_2026_UPDATED_t!$E:$E,$E7)</f>
-        <v>17512</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0.154065783462768</v>
-      </c>
-      <c r="L7">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C7,Data_Master_2015_2026_UPDATED_t!$E:$E,$E7)</f>
-        <v>2698</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>2023</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C8,Data_Master_2015_2026_UPDATED_t!$E:$E,$E8)</f>
-        <v>576</v>
-      </c>
-      <c r="H8">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C8,Data_Master_2015_2026_UPDATED_t!$E:$E,$E8)</f>
-        <v>224</v>
-      </c>
-      <c r="I8">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C8,Data_Master_2015_2026_UPDATED_t!$E:$E,$E8)</f>
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C8,Data_Master_2015_2026_UPDATED_t!$E:$E,$E8)</f>
-        <v>16328</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>0.0497305242528172</v>
-      </c>
-      <c r="L8">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C8,Data_Master_2015_2026_UPDATED_t!$E:$E,$E8)</f>
-        <v>812</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9">
-        <v>27</v>
-      </c>
-      <c r="E9">
-        <v>2022</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C9,Data_Master_2015_2026_UPDATED_t!$E:$E,$E9)</f>
-        <v>4732</v>
-      </c>
-      <c r="H9">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C9,Data_Master_2015_2026_UPDATED_t!$E:$E,$E9)</f>
-        <v>572</v>
-      </c>
-      <c r="I9">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C9,Data_Master_2015_2026_UPDATED_t!$E:$E,$E9)</f>
-        <v>162</v>
-      </c>
-      <c r="J9">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C9,Data_Master_2015_2026_UPDATED_t!$E:$E,$E9)</f>
-        <v>20058</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>0.27250972180676</v>
-      </c>
-      <c r="L9">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C9,Data_Master_2015_2026_UPDATED_t!$E:$E,$E9)</f>
-        <v>5466</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10">
-        <v>27</v>
-      </c>
-      <c r="E10">
-        <v>2022</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C10,Data_Master_2015_2026_UPDATED_t!$E:$E,$E10)</f>
-        <v>470</v>
-      </c>
-      <c r="H10">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C10,Data_Master_2015_2026_UPDATED_t!$E:$E,$E10)</f>
-        <v>214</v>
-      </c>
-      <c r="I10">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C10,Data_Master_2015_2026_UPDATED_t!$E:$E,$E10)</f>
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C10,Data_Master_2015_2026_UPDATED_t!$E:$E,$E10)</f>
-        <v>18134</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>0.0382706518142715</v>
-      </c>
-      <c r="L10">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C10,Data_Master_2015_2026_UPDATED_t!$E:$E,$E10)</f>
-        <v>694</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11">
-        <v>27</v>
-      </c>
-      <c r="E11">
-        <v>2021</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C11,Data_Master_2015_2026_UPDATED_t!$E:$E,$E11)</f>
-        <v>1014</v>
-      </c>
-      <c r="H11">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C11,Data_Master_2015_2026_UPDATED_t!$E:$E,$E11)</f>
-        <v>172</v>
-      </c>
-      <c r="I11">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C11,Data_Master_2015_2026_UPDATED_t!$E:$E,$E11)</f>
-        <v>26</v>
-      </c>
-      <c r="J11">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C11,Data_Master_2015_2026_UPDATED_t!$E:$E,$E11)</f>
-        <v>17970</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>0.0674457429048414</v>
-      </c>
-      <c r="L11">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C11,Data_Master_2015_2026_UPDATED_t!$E:$E,$E11)</f>
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12">
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <v>2021</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C12,Data_Master_2015_2026_UPDATED_t!$E:$E,$E12)</f>
-        <v>454</v>
-      </c>
-      <c r="H12">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C12,Data_Master_2015_2026_UPDATED_t!$E:$E,$E12)</f>
-        <v>220</v>
-      </c>
-      <c r="I12">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C12,Data_Master_2015_2026_UPDATED_t!$E:$E,$E12)</f>
-        <v>12</v>
-      </c>
-      <c r="J12">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!J:J,Data_Master_2015_2026_UPDATED_t!$C:$C,$C12,Data_Master_2015_2026_UPDATED_t!$E:$E,$E12)</f>
-        <v>16910</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>0.0405677114133649</v>
-      </c>
-      <c r="L12">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C12,Data_Master_2015_2026_UPDATED_t!$E:$E,$E12)</f>
-        <v>686</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13">
-        <v>27</v>
-      </c>
-      <c r="E13">
-        <v>2020</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C13,Data_Master_2015_2026_UPDATED_t!$E:$E,$E13)</f>
-        <v>2040</v>
-      </c>
-      <c r="H13">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C13,Data_Master_2015_2026_UPDATED_t!$E:$E,$E13)</f>
-        <v>3860</v>
-      </c>
-      <c r="I13">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C13,Data_Master_2015_2026_UPDATED_t!$E:$E,$E13)</f>
-        <v>88</v>
-      </c>
-      <c r="L13">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C13,Data_Master_2015_2026_UPDATED_t!$E:$E,$E13)</f>
-        <v>5988</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14">
-        <v>27</v>
-      </c>
-      <c r="E14">
-        <v>2020</v>
-      </c>
-      <c r="F14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C14,Data_Master_2015_2026_UPDATED_t!$E:$E,$E14)</f>
-        <v>484</v>
-      </c>
-      <c r="H14">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C14,Data_Master_2015_2026_UPDATED_t!$E:$E,$E14)</f>
-        <v>964</v>
-      </c>
-      <c r="I14">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C14,Data_Master_2015_2026_UPDATED_t!$E:$E,$E14)</f>
-        <v>14</v>
-      </c>
-      <c r="L14">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C14,Data_Master_2015_2026_UPDATED_t!$E:$E,$E14)</f>
-        <v>1462</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15">
-        <v>27</v>
-      </c>
-      <c r="E15">
-        <v>2019</v>
-      </c>
-      <c r="F15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C15,Data_Master_2015_2026_UPDATED_t!$E:$E,$E15)</f>
-        <v>2390</v>
-      </c>
-      <c r="H15">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C15,Data_Master_2015_2026_UPDATED_t!$E:$E,$E15)</f>
-        <v>42</v>
-      </c>
-      <c r="I15">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C15,Data_Master_2015_2026_UPDATED_t!$E:$E,$E15)</f>
-        <v>28</v>
-      </c>
-      <c r="L15">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C15,Data_Master_2015_2026_UPDATED_t!$E:$E,$E15)</f>
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16">
-        <v>27</v>
-      </c>
-      <c r="E16">
-        <v>2019</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C16,Data_Master_2015_2026_UPDATED_t!$E:$E,$E16)</f>
-        <v>588</v>
-      </c>
-      <c r="H16">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C16,Data_Master_2015_2026_UPDATED_t!$E:$E,$E16)</f>
-        <v>48</v>
-      </c>
-      <c r="I16">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C16,Data_Master_2015_2026_UPDATED_t!$E:$E,$E16)</f>
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C16,Data_Master_2015_2026_UPDATED_t!$E:$E,$E16)</f>
-        <v>636</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17">
-        <v>27</v>
-      </c>
-      <c r="E17">
-        <v>2018</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C17,Data_Master_2015_2026_UPDATED_t!$E:$E,$E17)</f>
-        <v>6940</v>
-      </c>
-      <c r="H17">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C17,Data_Master_2015_2026_UPDATED_t!$E:$E,$E17)</f>
-        <v>156</v>
-      </c>
-      <c r="I17">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C17,Data_Master_2015_2026_UPDATED_t!$E:$E,$E17)</f>
-        <v>74</v>
-      </c>
-      <c r="L17">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C17,Data_Master_2015_2026_UPDATED_t!$E:$E,$E17)</f>
-        <v>7170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18">
-        <v>27</v>
-      </c>
-      <c r="E18">
-        <v>2018</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C18,Data_Master_2015_2026_UPDATED_t!$E:$E,$E18)</f>
-        <v>472</v>
-      </c>
-      <c r="H18">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C18,Data_Master_2015_2026_UPDATED_t!$E:$E,$E18)</f>
-        <v>30</v>
-      </c>
-      <c r="I18">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C18,Data_Master_2015_2026_UPDATED_t!$E:$E,$E18)</f>
-        <v>30</v>
-      </c>
-      <c r="L18">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C18,Data_Master_2015_2026_UPDATED_t!$E:$E,$E18)</f>
-        <v>532</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19">
-        <v>27</v>
-      </c>
-      <c r="E19">
-        <v>2017</v>
-      </c>
-      <c r="F19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C19,Data_Master_2015_2026_UPDATED_t!$E:$E,$E19)</f>
-        <v>1792</v>
-      </c>
-      <c r="H19">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C19,Data_Master_2015_2026_UPDATED_t!$E:$E,$E19)</f>
-        <v>32</v>
-      </c>
-      <c r="I19">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C19,Data_Master_2015_2026_UPDATED_t!$E:$E,$E19)</f>
-        <v>44</v>
-      </c>
-      <c r="L19">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C19,Data_Master_2015_2026_UPDATED_t!$E:$E,$E19)</f>
-        <v>1868</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20">
-        <v>27</v>
-      </c>
-      <c r="E20">
-        <v>2017</v>
-      </c>
-      <c r="F20" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C20,Data_Master_2015_2026_UPDATED_t!$E:$E,$E20)</f>
-        <v>728</v>
-      </c>
-      <c r="H20">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C20,Data_Master_2015_2026_UPDATED_t!$E:$E,$E20)</f>
-        <v>28</v>
-      </c>
-      <c r="I20">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C20,Data_Master_2015_2026_UPDATED_t!$E:$E,$E20)</f>
-        <v>20</v>
-      </c>
-      <c r="L20">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C20,Data_Master_2015_2026_UPDATED_t!$E:$E,$E20)</f>
-        <v>776</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21">
-        <v>27</v>
-      </c>
-      <c r="E21">
-        <v>2016</v>
-      </c>
-      <c r="F21" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C21,Data_Master_2015_2026_UPDATED_t!$E:$E,$E21)</f>
-        <v>9790</v>
-      </c>
-      <c r="H21">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C21,Data_Master_2015_2026_UPDATED_t!$E:$E,$E21)</f>
-        <v>506</v>
-      </c>
-      <c r="I21">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C21,Data_Master_2015_2026_UPDATED_t!$E:$E,$E21)</f>
-        <v>140</v>
-      </c>
-      <c r="L21">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C21,Data_Master_2015_2026_UPDATED_t!$E:$E,$E21)</f>
-        <v>10436</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22">
-        <v>27</v>
-      </c>
-      <c r="E22">
-        <v>2016</v>
-      </c>
-      <c r="F22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C22,Data_Master_2015_2026_UPDATED_t!$E:$E,$E22)</f>
-        <v>4148</v>
-      </c>
-      <c r="H22">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C22,Data_Master_2015_2026_UPDATED_t!$E:$E,$E22)</f>
-        <v>44</v>
-      </c>
-      <c r="I22">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C22,Data_Master_2015_2026_UPDATED_t!$E:$E,$E22)</f>
-        <v>60</v>
-      </c>
-      <c r="L22">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C22,Data_Master_2015_2026_UPDATED_t!$E:$E,$E22)</f>
-        <v>4252</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23">
-        <v>27</v>
-      </c>
-      <c r="E23">
-        <v>2015</v>
-      </c>
-      <c r="F23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C23,Data_Master_2015_2026_UPDATED_t!$E:$E,$E23)</f>
-        <v>858</v>
-      </c>
-      <c r="H23">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C23,Data_Master_2015_2026_UPDATED_t!$E:$E,$E23)</f>
-        <v>8</v>
-      </c>
-      <c r="I23">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C23,Data_Master_2015_2026_UPDATED_t!$E:$E,$E23)</f>
-        <v>26</v>
-      </c>
-      <c r="L23">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C23,Data_Master_2015_2026_UPDATED_t!$E:$E,$E23)</f>
-        <v>892</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24">
-        <v>27</v>
-      </c>
-      <c r="E24">
-        <v>2015</v>
-      </c>
-      <c r="F24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C24,Data_Master_2015_2026_UPDATED_t!$E:$E,$E24)</f>
-        <v>476</v>
-      </c>
-      <c r="H24">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C24,Data_Master_2015_2026_UPDATED_t!$E:$E,$E24)</f>
-        <v>12</v>
-      </c>
-      <c r="I24">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C24,Data_Master_2015_2026_UPDATED_t!$E:$E,$E24)</f>
-        <v>22</v>
-      </c>
-      <c r="L24">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C24,Data_Master_2015_2026_UPDATED_t!$E:$E,$E24)</f>
-        <v>510</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25">
-        <v>27</v>
-      </c>
-      <c r="E25">
-        <v>2014</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C25,Data_Master_2015_2026_UPDATED_t!$E:$E,$E25)</f>
-        <v>280</v>
-      </c>
-      <c r="H25">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C25,Data_Master_2015_2026_UPDATED_t!$E:$E,$E25)</f>
-        <v>12</v>
-      </c>
-      <c r="I25">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C25,Data_Master_2015_2026_UPDATED_t!$E:$E,$E25)</f>
-        <v>4</v>
-      </c>
-      <c r="L25">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C25,Data_Master_2015_2026_UPDATED_t!$E:$E,$E25)</f>
-        <v>296</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26">
-        <v>27</v>
-      </c>
-      <c r="E26">
-        <v>2014</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!G:G,Data_Master_2015_2026_UPDATED_t!$C:$C,$C26,Data_Master_2015_2026_UPDATED_t!$E:$E,$E26)</f>
-        <v>2042</v>
-      </c>
-      <c r="H26">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!H:H,Data_Master_2015_2026_UPDATED_t!$C:$C,$C26,Data_Master_2015_2026_UPDATED_t!$E:$E,$E26)</f>
-        <v>20</v>
-      </c>
-      <c r="I26">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!I:I,Data_Master_2015_2026_UPDATED_t!$C:$C,$C26,Data_Master_2015_2026_UPDATED_t!$E:$E,$E26)</f>
-        <v>26</v>
-      </c>
-      <c r="L26">
-        <f>SUMIFS(Data_Master_2015_2026_UPDATED_t!L:L,Data_Master_2015_2026_UPDATED_t!$C:$C,$C26,Data_Master_2015_2026_UPDATED_t!$E:$E,$E26)</f>
-        <v>2088</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>